--- a/data/trans_orig/IQ2605_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IQ2605_R-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26735</t>
+          <t>26411</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40801</t>
+          <t>41112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>37733</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53885</t>
+          <t>53816</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>68832</t>
+          <t>68617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>91503</t>
+          <t>90603</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,08%</t>
+          <t>34,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>46,64%</t>
+          <t>46,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>27202</t>
+          <t>27572</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42214</t>
+          <t>42049</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>29660</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45368</t>
+          <t>45397</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>60456</t>
+          <t>61748</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>82854</t>
+          <t>82632</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,11%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11168</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>22705</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>23732</t>
+          <t>23351</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>25959</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42570</t>
+          <t>42863</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,23%</t>
+          <t>12,9%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -1112,7 +1112,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3407</t>
+          <t>3025</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1127,7 +1127,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,54%</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2181</t>
+          <t>2596</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2139</t>
+          <t>2093</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>6034</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>16494</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>49626</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>71595</t>
+          <t>71555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44629</t>
+          <t>43442</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65350</t>
+          <t>65022</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,47 +1465,47 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>114453</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>100988</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>130438</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>22,6%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
           <t>25,75%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>114453</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>99644</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>129696</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>22,6%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>19,67%</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>25,61%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>76377</t>
+          <t>78777</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>101504</t>
+          <t>101632</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>31,17%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>40,16%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68509</t>
+          <t>69303</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92547</t>
+          <t>93882</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>152766</t>
+          <t>154211</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186733</t>
+          <t>187155</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>36,87%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81721</t>
+          <t>81033</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>107074</t>
+          <t>104848</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>41,48%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>93068</t>
+          <t>93041</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>118243</t>
+          <t>119504</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>46,6%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>181715</t>
+          <t>181588</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>216321</t>
+          <t>215973</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,88%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>42,64%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3571</t>
+          <t>3466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12095</t>
+          <t>13116</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>4170</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12731</t>
+          <t>13715</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,02%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21302</t>
+          <t>21360</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1230</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7073</t>
+          <t>7631</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2828</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10659</t>
+          <t>11776</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,47 +1917,47 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>4,64%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>9208</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>5320</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>15293</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
           <t>1,05%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>4,2%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>9208</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>5300</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>15326</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>18624</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34489</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>27,04%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32958</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50256</t>
+          <t>50233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,51%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56070</t>
+          <t>55690</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>79013</t>
+          <t>78219</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,84%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26920</t>
+          <t>27332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>43329</t>
+          <t>42854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22526</t>
+          <t>22981</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38420</t>
+          <t>38755</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>27,15%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>54281</t>
+          <t>53745</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>76742</t>
+          <t>76360</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>28,52%</t>
+          <t>28,38%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>46723</t>
+          <t>46948</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>66227</t>
+          <t>64634</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>36,63%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>51,92%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>41516</t>
+          <t>42285</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>60600</t>
+          <t>60473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>29,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,73%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>92831</t>
+          <t>94922</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>119134</t>
+          <t>121100</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>44,28%</t>
+          <t>45,01%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3226</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10948</t>
+          <t>10942</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5092</t>
+          <t>5228</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>14547</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10258</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22357</t>
+          <t>22009</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,18%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2428</t>
+          <t>2632</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9872</t>
+          <t>10437</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5535</t>
+          <t>5754</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>16146</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,41%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>9963</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22041</t>
+          <t>21417</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>7,96%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>19253</t>
+          <t>19814</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35144</t>
+          <t>35198</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21505</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38082</t>
+          <t>37948</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>46386</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67835</t>
+          <t>68356</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>43675</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>63757</t>
+          <t>64161</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>33,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>45276</t>
+          <t>46042</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>65380</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,41%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>31,83%</t>
+          <t>32,84%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>94169</t>
+          <t>95558</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>122780</t>
+          <t>124457</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>23,57%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>74854</t>
+          <t>74259</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>95738</t>
+          <t>97343</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>50,15%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>75836</t>
+          <t>76667</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98892</t>
+          <t>99210</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>36,92%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>157609</t>
+          <t>157033</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>189448</t>
+          <t>188346</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>39,45%</t>
+          <t>39,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,14%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11176</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23545</t>
+          <t>23716</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15638</t>
+          <t>16237</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>30424</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>31220</t>
+          <t>31803</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>50572</t>
+          <t>50892</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,74%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6953</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18491</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5952</t>
+          <t>5459</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>16322</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15764</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>29991</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -3461,12 +3461,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>129814</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>164474</t>
+          <t>163087</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3476,12 +3476,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,75%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>153580</t>
+          <t>150294</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>189734</t>
+          <t>188756</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>290026</t>
+          <t>293204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>340761</t>
+          <t>341896</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>21,15%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>24,85%</t>
+          <t>24,93%</t>
         </is>
       </c>
     </row>
@@ -3574,12 +3574,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192111</t>
+          <t>192218</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>232941</t>
+          <t>232820</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,9%</t>
+          <t>28,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>35,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,12 +3609,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>184502</t>
+          <t>184486</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>222244</t>
+          <t>222935</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,7 +3629,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,12 +3644,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>387725</t>
+          <t>387796</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>441737</t>
+          <t>442687</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>32,21%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -3687,12 +3687,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>229279</t>
+          <t>228681</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>270982</t>
+          <t>270905</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3702,12 +3702,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,41%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,12 +3722,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>242833</t>
+          <t>241221</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>281982</t>
+          <t>283467</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3737,12 +3737,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>39,91%</t>
+          <t>40,12%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,12 +3757,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>484331</t>
+          <t>484525</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>543507</t>
+          <t>543345</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3772,12 +3772,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>35,32%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,62%</t>
         </is>
       </c>
     </row>
@@ -3800,12 +3800,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>22649</t>
+          <t>22382</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>40171</t>
+          <t>39697</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3835,12 +3835,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32728</t>
+          <t>31481</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>51148</t>
+          <t>51701</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3850,12 +3850,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3870,12 +3870,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>59937</t>
+          <t>58201</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>85529</t>
+          <t>85068</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,2%</t>
         </is>
       </c>
     </row>
@@ -3913,12 +3913,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>18539</t>
+          <t>18228</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>34262</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -3948,12 +3948,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>22773</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>40357</t>
+          <t>40336</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -3983,12 +3983,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>44124</t>
+          <t>45881</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>67615</t>
+          <t>69145</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3998,12 +3998,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,04%</t>
         </is>
       </c>
     </row>
@@ -4180,7 +4180,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2012 (tasa de respuesta: 99,66%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4375,12 +4375,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>73710</t>
+          <t>73917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>90349</t>
+          <t>89963</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>60237</t>
+          <t>61003</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78863</t>
+          <t>78064</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>140604</t>
+          <t>138931</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165518</t>
+          <t>163928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4460,12 +4460,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>57,83%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>67,42%</t>
         </is>
       </c>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18486</t>
+          <t>18180</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32712</t>
+          <t>31629</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4503,12 +4503,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4523,12 +4523,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28235</t>
+          <t>28699</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>45022</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4538,12 +4538,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,18%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4558,12 +4558,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49302</t>
+          <t>50073</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>72518</t>
+          <t>72644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4573,12 +4573,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,88%</t>
         </is>
       </c>
     </row>
@@ -4601,12 +4601,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5778</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>15455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4616,12 +4616,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4636,12 +4636,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3099</t>
+          <t>3521</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11866</t>
+          <t>11989</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4671,12 +4671,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>10037</t>
+          <t>10486</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>23001</t>
+          <t>24175</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4686,12 +4686,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,94%</t>
         </is>
       </c>
     </row>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3576</t>
+          <t>3589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4734,7 +4734,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4789,7 +4789,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4294</t>
+          <t>4137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4827,12 +4827,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>4321</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>12792</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4862,12 +4862,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>2055</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10442</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4877,12 +4877,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4897,12 +4897,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7640</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19013</t>
+          <t>19263</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4912,12 +4912,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>7,92%</t>
         </is>
       </c>
     </row>
@@ -5057,12 +5057,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>81381</t>
+          <t>82821</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106812</t>
+          <t>108313</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5072,12 +5072,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5092,12 +5092,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>90829</t>
+          <t>91493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>118146</t>
+          <t>118293</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5107,12 +5107,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,03%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5127,12 +5127,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>178333</t>
+          <t>180022</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216043</t>
+          <t>215669</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5142,12 +5142,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,34%</t>
+          <t>35,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -5170,12 +5170,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>75119</t>
+          <t>74012</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99666</t>
+          <t>98974</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5185,12 +5185,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>41,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5205,12 +5205,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92779</t>
+          <t>91670</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>120118</t>
+          <t>118338</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5220,12 +5220,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>34,58%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,1%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5240,12 +5240,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>173649</t>
+          <t>173415</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>210882</t>
+          <t>210703</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5255,12 +5255,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,42%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>41,76%</t>
         </is>
       </c>
     </row>
@@ -5283,12 +5283,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>35716</t>
+          <t>35967</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56076</t>
+          <t>56108</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5298,12 +5298,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5318,12 +5318,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56400</t>
+          <t>54937</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5333,12 +5333,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>76159</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>106235</t>
+          <t>105308</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5368,12 +5368,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>21,05%</t>
+          <t>20,87%</t>
         </is>
       </c>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1357</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8049</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5411,12 +5411,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5431,12 +5431,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3239</t>
+          <t>2974</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11241</t>
+          <t>11531</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5446,12 +5446,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5466,12 +5466,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5691</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17276</t>
+          <t>17416</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5481,12 +5481,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5509,12 +5509,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2737</t>
+          <t>2844</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11583</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5524,12 +5524,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5544,12 +5544,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4508</t>
+          <t>4266</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14858</t>
+          <t>14987</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5559,12 +5559,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5579,12 +5579,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>8511</t>
+          <t>8838</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>22240</t>
+          <t>23102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -5739,12 +5739,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>43084</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>62810</t>
+          <t>63516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5754,12 +5754,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5774,12 +5774,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>40167</t>
+          <t>39902</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>59293</t>
+          <t>59226</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5789,12 +5789,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5809,12 +5809,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>87149</t>
+          <t>88274</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>114617</t>
+          <t>116379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5824,12 +5824,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -5852,12 +5852,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54117</t>
+          <t>53561</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74157</t>
+          <t>73479</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5867,12 +5867,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>34,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,59%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5887,12 +5887,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43106</t>
+          <t>43007</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>63079</t>
+          <t>61721</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5902,12 +5902,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,18%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5922,12 +5922,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>101758</t>
+          <t>100407</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>129941</t>
+          <t>129189</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5937,12 +5937,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,09%</t>
         </is>
       </c>
     </row>
@@ -5965,12 +5965,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20996</t>
+          <t>20848</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>36364</t>
+          <t>36630</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5980,12 +5980,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6000,12 +6000,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31056</t>
+          <t>31744</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>49058</t>
+          <t>50574</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6015,12 +6015,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6035,12 +6035,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57671</t>
+          <t>57912</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>81377</t>
+          <t>82758</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,32%</t>
         </is>
       </c>
     </row>
@@ -6078,12 +6078,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3090</t>
+          <t>3060</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>12746</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6093,12 +6093,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3236</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12192</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8170</t>
+          <t>8551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>20947</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -6191,12 +6191,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>9804</t>
+          <t>9905</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6206,12 +6206,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>5952</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16520</t>
+          <t>17184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>9875</t>
+          <t>9855</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22330</t>
+          <t>23448</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -6421,12 +6421,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>31798</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>50710</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6436,12 +6436,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6456,12 +6456,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>31905</t>
+          <t>31494</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51103</t>
+          <t>49704</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,4%</t>
+          <t>27,62%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69672</t>
+          <t>69380</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>95747</t>
+          <t>96222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,45%</t>
         </is>
       </c>
     </row>
@@ -6534,12 +6534,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>50837</t>
+          <t>51381</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>72058</t>
+          <t>72246</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6549,12 +6549,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6569,12 +6569,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>63179</t>
+          <t>63711</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>84773</t>
+          <t>84208</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,11%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>47,11%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>121188</t>
+          <t>120193</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>151431</t>
+          <t>150300</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,57%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,88%</t>
         </is>
       </c>
     </row>
@@ -6647,12 +6647,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>43331</t>
+          <t>42502</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>63511</t>
+          <t>62297</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6662,12 +6662,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>37,23%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6682,12 +6682,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>36225</t>
+          <t>36783</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>54705</t>
+          <t>56684</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6697,12 +6697,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>31,5%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6717,12 +6717,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>84948</t>
+          <t>85227</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>112804</t>
+          <t>110885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,31%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -6760,12 +6760,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3466</t>
+          <t>3570</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13135</t>
+          <t>12839</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6795,12 +6795,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2795</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12102</t>
+          <t>11889</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6830,12 +6830,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20513</t>
+          <t>20258</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6845,12 +6845,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -6873,12 +6873,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13923</t>
+          <t>14891</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7877</t>
+          <t>8386</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>20218</t>
+          <t>19931</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6923,12 +6923,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6943,12 +6943,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>15555</t>
+          <t>15914</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>30155</t>
+          <t>29903</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6958,12 +6958,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,53%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>248148</t>
+          <t>249399</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>288307</t>
+          <t>292892</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>36,07%</t>
+          <t>36,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>240824</t>
+          <t>239807</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>284837</t>
+          <t>285405</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>500460</t>
+          <t>503087</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>561893</t>
+          <t>562617</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,43%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,78%</t>
+          <t>39,83%</t>
         </is>
       </c>
     </row>
@@ -7216,12 +7216,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>216803</t>
+          <t>216620</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>257248</t>
+          <t>257393</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,49%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>37,4%</t>
+          <t>37,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7251,12 +7251,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>246004</t>
+          <t>247673</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>289936</t>
+          <t>291858</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7266,12 +7266,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,17%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,0%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7286,12 +7286,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>471161</t>
+          <t>473190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>534043</t>
+          <t>533764</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7301,12 +7301,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,5%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>37,78%</t>
         </is>
       </c>
     </row>
@@ -7329,12 +7329,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>119133</t>
+          <t>117337</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>153827</t>
+          <t>153101</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7344,12 +7344,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7364,12 +7364,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>120420</t>
+          <t>119918</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>155470</t>
+          <t>154940</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7379,12 +7379,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,55%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7399,12 +7399,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>250425</t>
+          <t>249670</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>298128</t>
+          <t>300277</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>21,26%</t>
         </is>
       </c>
     </row>
@@ -7442,12 +7442,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12432</t>
+          <t>12171</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7457,12 +7457,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7477,12 +7477,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>13481</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>28046</t>
+          <t>27337</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7492,12 +7492,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7512,12 +7512,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>29200</t>
+          <t>29060</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>49201</t>
+          <t>50134</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,55%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>20182</t>
+          <t>19238</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>37912</t>
+          <t>37129</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -7590,12 +7590,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28505</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>49284</t>
+          <t>48600</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7605,12 +7605,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>52786</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>77663</t>
+          <t>78657</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,57%</t>
         </is>
       </c>
     </row>
@@ -7822,7 +7822,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2016 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8017,12 +8017,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61636</t>
+          <t>61237</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77980</t>
+          <t>78706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8032,12 +8032,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,54%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55771</t>
+          <t>55723</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72972</t>
+          <t>72422</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8067,12 +8067,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>120822</t>
+          <t>122142</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>145455</t>
+          <t>147259</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8102,12 +8102,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>51,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,25%</t>
+          <t>62,01%</t>
         </is>
       </c>
     </row>
@@ -8130,12 +8130,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>15092</t>
+          <t>15110</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27524</t>
+          <t>28004</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8145,12 +8145,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8165,12 +8165,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22535</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>36693</t>
+          <t>36941</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8180,12 +8180,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,26%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>31,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8200,12 +8200,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40878</t>
+          <t>40911</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>60633</t>
+          <t>60018</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>25,27%</t>
         </is>
       </c>
     </row>
@@ -8243,12 +8243,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1780</t>
+          <t>2107</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9225</t>
+          <t>9703</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8258,12 +8258,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8278,12 +8278,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>1454</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8911</t>
+          <t>8320</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8293,12 +8293,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8313,12 +8313,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>4815</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>14253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8328,12 +8328,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -8361,7 +8361,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3019</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8376,7 +8376,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8396,7 +8396,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4306</t>
+          <t>4863</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8411,7 +8411,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8426,12 +8426,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6023</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -8469,12 +8469,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18519</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31985</t>
+          <t>32763</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8484,12 +8484,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8504,12 +8504,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11697</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23836</t>
+          <t>23282</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8519,12 +8519,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8539,12 +8539,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>33145</t>
+          <t>31872</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>51934</t>
+          <t>50940</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -8699,12 +8699,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87529</t>
+          <t>86991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110569</t>
+          <t>110500</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8714,12 +8714,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,49%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8734,12 +8734,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97499</t>
+          <t>98861</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>123860</t>
+          <t>124325</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8749,12 +8749,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8769,12 +8769,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>192422</t>
+          <t>194436</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>227175</t>
+          <t>227062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8784,12 +8784,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,46%</t>
         </is>
       </c>
     </row>
@@ -8812,12 +8812,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67838</t>
+          <t>66961</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89544</t>
+          <t>89323</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8827,12 +8827,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,43%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8847,12 +8847,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94710</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>119620</t>
+          <t>120355</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8862,12 +8862,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,7%</t>
+          <t>36,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8882,12 +8882,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>167765</t>
+          <t>167809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>204354</t>
+          <t>200501</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8897,12 +8897,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>42,79%</t>
         </is>
       </c>
     </row>
@@ -8925,12 +8925,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>16798</t>
+          <t>16903</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>31239</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8940,12 +8940,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8960,12 +8960,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21074</t>
+          <t>21006</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>37434</t>
+          <t>37634</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40942</t>
+          <t>41879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62829</t>
+          <t>63887</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9010,12 +9010,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -9038,12 +9038,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3129</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>12256</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9073,12 +9073,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9088,12 +9088,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9108,12 +9108,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>15954</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9123,12 +9123,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -9151,12 +9151,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1377</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9166,12 +9166,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14244</t>
+          <t>14771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9201,12 +9201,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9221,12 +9221,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7935</t>
+          <t>7896</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18841</t>
+          <t>19452</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9241,7 +9241,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
     </row>
@@ -9381,12 +9381,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>67133</t>
+          <t>67434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89921</t>
+          <t>88716</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>66091</t>
+          <t>64898</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>88314</t>
+          <t>87628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,05%</t>
+          <t>34,42%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>138535</t>
+          <t>138266</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>168791</t>
+          <t>171181</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9466,12 +9466,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>45,41%</t>
         </is>
       </c>
     </row>
@@ -9494,12 +9494,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52872</t>
+          <t>53462</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74630</t>
+          <t>76070</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9509,12 +9509,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9529,12 +9529,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59753</t>
+          <t>59702</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>81618</t>
+          <t>82059</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>118186</t>
+          <t>118297</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>149321</t>
+          <t>150031</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9579,12 +9579,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>39,8%</t>
         </is>
       </c>
     </row>
@@ -9607,12 +9607,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>28131</t>
+          <t>28391</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47124</t>
+          <t>46684</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>15,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9642,12 +9642,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25521</t>
+          <t>26145</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>43125</t>
+          <t>42784</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9657,12 +9657,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>22,87%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9677,12 +9677,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>57946</t>
+          <t>58248</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>83115</t>
+          <t>83103</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9692,12 +9692,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -9720,12 +9720,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2116</t>
+          <t>2623</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10090</t>
+          <t>10317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9735,12 +9735,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>945</t>
+          <t>946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7841</t>
+          <t>7919</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9790,12 +9790,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4821</t>
+          <t>4632</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15524</t>
+          <t>14374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9805,12 +9805,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,81%</t>
         </is>
       </c>
     </row>
@@ -9833,12 +9833,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1873</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>8745</t>
+          <t>8827</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9848,12 +9848,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>1456</t>
+          <t>1437</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>8452</t>
+          <t>8436</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9883,12 +9883,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9903,12 +9903,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4505</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14186</t>
+          <t>14469</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9918,12 +9918,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -10063,12 +10063,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>54148</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>75607</t>
+          <t>74004</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10078,12 +10078,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>43,87%</t>
+          <t>42,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44301</t>
+          <t>45017</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>65291</t>
+          <t>66390</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10113,12 +10113,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,86%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,51%</t>
+          <t>38,14%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>106164</t>
+          <t>105612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>134671</t>
+          <t>133292</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10148,12 +10148,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,49%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>38,48%</t>
         </is>
       </c>
     </row>
@@ -10176,12 +10176,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>43109</t>
+          <t>42641</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62784</t>
+          <t>63576</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10191,12 +10191,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>36,89%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>58291</t>
+          <t>58945</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>79618</t>
+          <t>80806</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10226,12 +10226,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,49%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10246,12 +10246,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>107981</t>
+          <t>108045</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>137759</t>
+          <t>135524</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10261,12 +10261,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>39,12%</t>
         </is>
       </c>
     </row>
@@ -10289,12 +10289,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33375</t>
+          <t>33326</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>52089</t>
+          <t>52935</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10304,12 +10304,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>19,37%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10324,12 +10324,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>28204</t>
+          <t>28048</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>45842</t>
+          <t>47440</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10339,12 +10339,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10359,12 +10359,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>66428</t>
+          <t>66993</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>92243</t>
+          <t>92407</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10374,12 +10374,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,18%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,68%</t>
         </is>
       </c>
     </row>
@@ -10402,12 +10402,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2048</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>10111</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10422,7 +10422,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10437,12 +10437,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2802</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11715</t>
+          <t>11227</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10452,12 +10452,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10472,12 +10472,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>6352</t>
+          <t>6398</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18051</t>
+          <t>17859</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10487,12 +10487,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -10515,12 +10515,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4501</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>15475</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10530,12 +10530,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10550,12 +10550,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3454</t>
+          <t>3425</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>11982</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10565,12 +10565,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10585,12 +10585,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9459</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>22680</t>
+          <t>23109</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10600,12 +10600,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>289190</t>
+          <t>289028</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>330856</t>
+          <t>331981</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10760,12 +10760,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>47,97%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10780,12 +10780,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>284191</t>
+          <t>283558</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>329216</t>
+          <t>330620</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,46%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>44,65%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10815,12 +10815,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>589725</t>
+          <t>589881</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>648829</t>
+          <t>652717</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,27%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,66%</t>
         </is>
       </c>
     </row>
@@ -10858,12 +10858,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>195679</t>
+          <t>196518</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>236564</t>
+          <t>235578</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>34,18%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10893,12 +10893,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>253979</t>
+          <t>254779</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>296341</t>
+          <t>298620</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10908,12 +10908,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,55%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>40,5%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10928,12 +10928,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>460727</t>
+          <t>459659</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>521830</t>
+          <t>520742</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -10971,12 +10971,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>92434</t>
+          <t>92878</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>124332</t>
+          <t>122114</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10986,12 +10986,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11006,12 +11006,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>87494</t>
+          <t>87409</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>118798</t>
+          <t>119125</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11021,12 +11021,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,11%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11041,12 +11041,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>188678</t>
+          <t>187301</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>232207</t>
+          <t>233160</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11056,12 +11056,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,31%</t>
         </is>
       </c>
     </row>
@@ -11084,12 +11084,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>11368</t>
+          <t>11324</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>24936</t>
+          <t>25230</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11119,12 +11119,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>8446</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>21195</t>
+          <t>22100</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11134,12 +11134,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11154,12 +11154,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>23177</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>41721</t>
+          <t>41537</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,91%</t>
         </is>
       </c>
     </row>
@@ -11197,12 +11197,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>31990</t>
+          <t>32089</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>52429</t>
+          <t>53653</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11212,12 +11212,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11232,12 +11232,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>28249</t>
+          <t>28700</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>47858</t>
+          <t>47675</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11247,12 +11247,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11267,12 +11267,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>65588</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>93013</t>
+          <t>93371</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11282,12 +11282,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>6,53%</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si hacen uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
+          <t>Menores según si el verano pasado hicieron uso de la sombra para evitar el sol en 2023 (tasa de respuesta: 99,58%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -11659,12 +11659,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4877</t>
+          <t>4900</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10072</t>
+          <t>10572</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -11674,12 +11674,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>35,46%</t>
+          <t>35,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>76,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11694,12 +11694,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5969</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11620</t>
+          <t>11519</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,2%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11729,12 +11729,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>12548</t>
+          <t>12394</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20480</t>
+          <t>20490</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11744,12 +11744,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>73,02%</t>
         </is>
       </c>
     </row>
@@ -11772,12 +11772,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2682</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11787,12 +11787,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,51%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>58,42%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11807,12 +11807,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>1360</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6101</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11822,12 +11822,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>41,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11842,12 +11842,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5153</t>
+          <t>5380</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11857,12 +11857,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>44,01%</t>
+          <t>45,38%</t>
         </is>
       </c>
     </row>
@@ -11890,7 +11890,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3107</t>
+          <t>2927</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11925,7 +11925,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4958</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11940,7 +11940,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>36,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11955,12 +11955,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5568</t>
+          <t>5553</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11970,12 +11970,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,79%</t>
         </is>
       </c>
     </row>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -12053,7 +12053,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>26,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3773</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>12,97%</t>
         </is>
       </c>
     </row>
@@ -12341,12 +12341,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>7128</t>
+          <t>6717</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16837</t>
+          <t>16336</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -12376,12 +12376,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>11190</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -12391,12 +12391,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -12411,12 +12411,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19868</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>35000</t>
+          <t>34865</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -12426,12 +12426,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>44,07%</t>
         </is>
       </c>
     </row>
@@ -12454,12 +12454,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13607</t>
+          <t>13510</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>22891</t>
+          <t>23314</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -12469,12 +12469,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,63%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>67,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -12489,12 +12489,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17372</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>28319</t>
+          <t>28695</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -12504,12 +12504,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -12524,12 +12524,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>33653</t>
+          <t>33886</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>49218</t>
+          <t>48668</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -12539,12 +12539,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>61,52%</t>
         </is>
       </c>
     </row>
@@ -12567,12 +12567,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2577</t>
+          <t>2561</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8846</t>
+          <t>9128</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -12582,12 +12582,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -12602,12 +12602,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2743</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9748</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -12617,12 +12617,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -12637,12 +12637,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6667</t>
+          <t>6879</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16083</t>
+          <t>16449</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -12652,12 +12652,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,79%</t>
         </is>
       </c>
     </row>
@@ -13023,12 +13023,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2846</t>
+          <t>2600</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10577</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -13038,12 +13038,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -13058,12 +13058,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6858</t>
+          <t>7194</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20018</t>
+          <t>20455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -13073,12 +13073,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>36,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -13093,12 +13093,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26814</t>
+          <t>26880</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -13108,12 +13108,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,02%</t>
         </is>
       </c>
     </row>
@@ -13136,12 +13136,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16980</t>
+          <t>16747</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>28615</t>
+          <t>29345</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -13151,12 +13151,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>73,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -13171,12 +13171,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19167</t>
+          <t>19493</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>34090</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -13186,12 +13186,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,28%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,97%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -13206,12 +13206,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>39312</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>58468</t>
+          <t>58711</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -13221,12 +13221,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>40,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -13249,12 +13249,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5193</t>
+          <t>4818</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>14115</t>
+          <t>13860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -13264,12 +13264,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,98%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>35,28%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -13284,12 +13284,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9879</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>21734</t>
+          <t>21914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -13299,12 +13299,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>38,87%</t>
+          <t>39,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -13319,12 +13319,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17424</t>
+          <t>17439</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>32445</t>
+          <t>33601</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>18,18%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>35,03%</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6608</t>
+          <t>7221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -13382,7 +13382,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -13402,7 +13402,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4188</t>
+          <t>4049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -13432,12 +13432,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>772</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -13515,7 +13515,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>5573</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -13530,7 +13530,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -13550,7 +13550,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -13565,7 +13565,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -13705,12 +13705,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8219</t>
+          <t>8563</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>19026</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13720,12 +13720,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>34,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>9143</t>
+          <t>8856</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>20946</t>
+          <t>21523</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13755,12 +13755,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>27,28%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20419</t>
+          <t>19413</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36120</t>
+          <t>35770</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -13818,12 +13818,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>14024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25020</t>
+          <t>25558</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -13833,12 +13833,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>46,47%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>33128</t>
+          <t>32829</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>50569</t>
+          <t>50281</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -13868,12 +13868,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>42,76%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,86%</t>
+          <t>65,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>51246</t>
+          <t>49431</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71938</t>
+          <t>71753</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -13903,12 +13903,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,59%</t>
+          <t>54,45%</t>
         </is>
       </c>
     </row>
@@ -13931,12 +13931,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>11998</t>
+          <t>11540</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22962</t>
+          <t>22956</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13946,12 +13946,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -13966,12 +13966,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>10561</t>
+          <t>10846</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>23849</t>
+          <t>24701</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13981,12 +13981,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -14001,12 +14001,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25722</t>
+          <t>25121</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>43029</t>
+          <t>42528</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -14016,12 +14016,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>32,65%</t>
+          <t>32,27%</t>
         </is>
       </c>
     </row>
@@ -14044,12 +14044,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7760</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4820</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -14099,7 +14099,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -14114,12 +14114,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1589</t>
+          <t>1630</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>9583</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -14129,12 +14129,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -14157,12 +14157,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>711</t>
+          <t>745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>6845</t>
+          <t>6688</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -14172,12 +14172,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -14192,12 +14192,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>595</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9912</t>
+          <t>9664</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -14207,12 +14207,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -14227,12 +14227,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>12290</t>
+          <t>12828</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -14242,12 +14242,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -14387,12 +14387,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29311</t>
+          <t>28383</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>46904</t>
+          <t>45672</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -14402,12 +14402,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -14422,12 +14422,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>40665</t>
+          <t>40856</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>63416</t>
+          <t>63650</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -14437,12 +14437,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -14457,12 +14457,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>76423</t>
+          <t>74911</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>104199</t>
+          <t>104172</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -14472,12 +14472,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>22,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -14500,12 +14500,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>56193</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>76511</t>
+          <t>75672</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -14515,12 +14515,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -14535,12 +14535,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>83493</t>
+          <t>81806</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>109368</t>
+          <t>108422</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -14550,12 +14550,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,66%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>57,03%</t>
+          <t>56,54%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -14570,12 +14570,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>145205</t>
+          <t>142664</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>177071</t>
+          <t>180259</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -14585,12 +14585,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>43,36%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -14613,12 +14613,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24086</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>39754</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -14628,12 +14628,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -14648,12 +14648,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>28943</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50535</t>
+          <t>49754</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -14663,12 +14663,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15,42%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -14683,12 +14683,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>57188</t>
+          <t>58332</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>83553</t>
+          <t>83353</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14698,12 +14698,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>17,08%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,89%</t>
         </is>
       </c>
     </row>
@@ -14726,12 +14726,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>2749</t>
+          <t>2677</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11769</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14741,12 +14741,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -14761,12 +14761,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>735</t>
+          <t>734</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>6610</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14781,7 +14781,7 @@
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -14796,12 +14796,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4194</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14542</t>
+          <t>14326</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -14839,12 +14839,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>704</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6946</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -14854,12 +14854,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -14874,12 +14874,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>1460</t>
+          <t>941</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>10607</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -14889,12 +14889,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -14909,12 +14909,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>3232</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>14581</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -14924,12 +14924,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
